--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260924.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:19</t>
+          <t>2026-09-24 08:43:39</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">

--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260924.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:39</t>
+          <t>2026-09-24 13:44:16</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
